--- a/yh/project/20260407/XX支行——4月结存需求汇总.xlsx
+++ b/yh/project/20260407/XX支行——4月结存需求汇总.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="9195" firstSheet="3" activeTab="2"/>
+    <workbookView windowWidth="20400" windowHeight="9390" firstSheet="3" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="跨月私募" sheetId="4" r:id="rId1"/>
@@ -1566,20 +1566,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J2156"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.3716814159292" style="4" customWidth="1"/>
-    <col min="2" max="2" width="37.1504424778761" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="37.15" style="4" customWidth="1"/>
     <col min="3" max="3" width="17" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.3716814159292" style="4" customWidth="1"/>
-    <col min="5" max="6" width="15.6283185840708" style="5" customWidth="1"/>
+    <col min="4" max="4" width="13.375" style="4" customWidth="1"/>
+    <col min="5" max="6" width="15.625" style="5" customWidth="1"/>
     <col min="7" max="7" width="13" style="4" customWidth="1"/>
-    <col min="8" max="8" width="24.1238938053097" style="4" customWidth="1"/>
-    <col min="9" max="9" width="25.1238938053097" style="4" customWidth="1"/>
-    <col min="10" max="10" width="20.6283185840708" customWidth="1"/>
+    <col min="8" max="8" width="24.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="25.125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="66" spans="1:10">
+    <row r="1" ht="54" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10548,7 +10548,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"1M,2M,3M,6M,9M,12M"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F48 G2:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:H48 G49:H1048576">
       <formula1>"否,是"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10561,20 +10561,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.87610619469027" style="27" customWidth="1"/>
-    <col min="2" max="2" width="31.5575221238938" style="27" customWidth="1"/>
-    <col min="3" max="3" width="18.6283185840708" style="27" customWidth="1"/>
-    <col min="4" max="4" width="25.1327433628319" style="27" customWidth="1"/>
-    <col min="5" max="7" width="17.8761061946903" style="27" customWidth="1"/>
-    <col min="8" max="8" width="12.6283185840708" style="27" customWidth="1"/>
-    <col min="9" max="9" width="8.6283185840708" style="27" customWidth="1"/>
-    <col min="10" max="10" width="12.6283185840708" style="27" customWidth="1"/>
+    <col min="1" max="1" width="9.875" style="27" customWidth="1"/>
+    <col min="2" max="2" width="31.5583333333333" style="27" customWidth="1"/>
+    <col min="3" max="3" width="18.625" style="27" customWidth="1"/>
+    <col min="4" max="4" width="25.1333333333333" style="27" customWidth="1"/>
+    <col min="5" max="7" width="17.875" style="27" customWidth="1"/>
+    <col min="8" max="8" width="12.625" style="27" customWidth="1"/>
+    <col min="9" max="9" width="8.625" style="27" customWidth="1"/>
+    <col min="10" max="10" width="12.625" style="27" customWidth="1"/>
     <col min="11" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="49.5" spans="1:10">
+    <row r="1" ht="40.5" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10775,19 +10775,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I1259"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.3716814159292" style="4" customWidth="1"/>
-    <col min="2" max="2" width="31.3716814159292" style="4" customWidth="1"/>
-    <col min="3" max="4" width="14.6283185840708" style="4" customWidth="1"/>
-    <col min="5" max="5" width="19.8141592920354" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.8761061946903" style="5" customWidth="1"/>
-    <col min="7" max="7" width="14.0973451327434" style="4" customWidth="1"/>
-    <col min="8" max="8" width="17.6283185840708" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.6283185840708" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="31.375" style="4" customWidth="1"/>
+    <col min="3" max="4" width="14.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="19.8166666666667" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="14.1" style="4" customWidth="1"/>
+    <col min="8" max="8" width="17.625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.75" spans="1:9">
+    <row r="1" ht="27.75" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -10835,7 +10835,7 @@
       <c r="H2" s="14"/>
       <c r="I2" s="14"/>
     </row>
-    <row r="3" ht="17.25" spans="1:9">
+    <row r="3" ht="14.25" spans="1:9">
       <c r="A3" s="15" t="s">
         <v>26</v>
       </c>
@@ -17015,13 +17015,13 @@
     <mergeCell ref="D2:D3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4 E2:E3 E5:E301">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E301">
       <formula1>"14D,21D,28D"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4 G2:G3 G5:G1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>"账上资金,新引入资金，月底前到账,下月初到账"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4 H2:H3 H5:H1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17034,17 +17034,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="9.87610619469027" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.5575221238938" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5044247787611" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1327433628319" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.8761061946903" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.2477876106195" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.5583333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5083333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="49.5" spans="1:6">
+    <row r="1" ht="40.5" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
